--- a/დეკლარაცია დელივერერს.xlsx
+++ b/დეკლარაცია დელივერერს.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\nana\bank-summary\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{884FB434-6D48-4BDD-9C82-06E495CFDC86}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{441A1C9B-D5CF-4729-BE2C-A20615BD4900}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="23040" windowHeight="8940" tabRatio="889" firstSheet="30" activeTab="44" xr2:uid="{262C77A9-C0EF-4E18-A530-ED4A8457AF6E}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="23040" windowHeight="8940" tabRatio="889" firstSheet="32" activeTab="46" xr2:uid="{262C77A9-C0EF-4E18-A530-ED4A8457AF6E}"/>
   </bookViews>
   <sheets>
     <sheet name="კალკულაცია აგვისტო" sheetId="3" r:id="rId1"/>
@@ -58,6 +58,8 @@
     <sheet name="მარ 26" sheetId="45" r:id="rId43"/>
     <sheet name="აპრილი 26" sheetId="46" r:id="rId44"/>
     <sheet name="მაისი 26" sheetId="47" r:id="rId45"/>
+    <sheet name="ივნისი 26" sheetId="48" r:id="rId46"/>
+    <sheet name="ივლისი 26" sheetId="49" r:id="rId47"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -69,7 +71,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="336" uniqueCount="69">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="348" uniqueCount="71">
   <si>
     <t>დელივერერს</t>
   </si>
@@ -276,6 +278,12 @@
   </si>
   <si>
     <t>ცელერისი</t>
+  </si>
+  <si>
+    <t>ჩთ</t>
+  </si>
+  <si>
+    <t>საწვ</t>
   </si>
 </sst>
 </file>
@@ -4958,6 +4966,242 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet46.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CA10AD3D-9237-4918-A172-0004673ABC91}">
+  <dimension ref="B5:J15"/>
+  <sheetFormatPr defaultRowHeight="14.4"/>
+  <cols>
+    <col min="2" max="2" width="13.77734375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="10.109375" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="10.44140625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="10.109375" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="10.21875" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="10.44140625" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="5" spans="2:10">
+      <c r="B5" s="4" t="s">
+        <v>36</v>
+      </c>
+      <c r="C5" s="4">
+        <v>86637.01</v>
+      </c>
+      <c r="D5" s="5">
+        <f>C5/1.18</f>
+        <v>73421.194915254237</v>
+      </c>
+      <c r="E5" s="4">
+        <f>D5*0.18</f>
+        <v>13215.815084745762</v>
+      </c>
+      <c r="G5" t="s">
+        <v>4</v>
+      </c>
+      <c r="H5" s="4">
+        <v>12687</v>
+      </c>
+    </row>
+    <row r="6" spans="2:10">
+      <c r="B6" s="4"/>
+      <c r="C6" s="4"/>
+      <c r="D6" s="5"/>
+      <c r="E6" s="4">
+        <f>E5-C9</f>
+        <v>12687.285084745761</v>
+      </c>
+      <c r="G6" t="s">
+        <v>39</v>
+      </c>
+      <c r="H6" s="5">
+        <f>1637.82-200</f>
+        <v>1437.82</v>
+      </c>
+    </row>
+    <row r="7" spans="2:10">
+      <c r="B7" s="4"/>
+      <c r="C7" s="4">
+        <v>244.35</v>
+      </c>
+      <c r="D7" s="56"/>
+      <c r="E7" s="4"/>
+      <c r="G7" t="s">
+        <v>67</v>
+      </c>
+      <c r="H7" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" spans="2:10">
+      <c r="B8" s="4"/>
+      <c r="C8" s="4">
+        <v>284.18</v>
+      </c>
+      <c r="D8" s="56"/>
+      <c r="E8" s="4"/>
+      <c r="H8" s="58">
+        <f>SUM(H5:H7)</f>
+        <v>14124.82</v>
+      </c>
+      <c r="I8">
+        <v>14124.82</v>
+      </c>
+      <c r="J8" s="9">
+        <f>I8-H8</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="2:10">
+      <c r="B9" s="4"/>
+      <c r="C9" s="5">
+        <f>SUM(C7:C8)</f>
+        <v>528.53</v>
+      </c>
+      <c r="D9" s="4"/>
+      <c r="E9" s="4"/>
+      <c r="H9" s="59"/>
+    </row>
+    <row r="10" spans="2:10">
+      <c r="G10" s="25" t="s">
+        <v>68</v>
+      </c>
+      <c r="H10" s="58">
+        <v>200</v>
+      </c>
+      <c r="I10" s="9"/>
+    </row>
+    <row r="11" spans="2:10">
+      <c r="C11" s="48"/>
+      <c r="H11" s="59"/>
+    </row>
+    <row r="12" spans="2:10">
+      <c r="H12" s="59"/>
+    </row>
+    <row r="13" spans="2:10">
+      <c r="H13" s="59"/>
+    </row>
+    <row r="14" spans="2:10">
+      <c r="H14" s="25"/>
+    </row>
+    <row r="15" spans="2:10">
+      <c r="H15" s="25"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet47.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F7C248A0-1FED-4D18-85F7-C5EA58116720}">
+  <dimension ref="B5:J15"/>
+  <sheetFormatPr defaultRowHeight="14.4"/>
+  <cols>
+    <col min="2" max="2" width="13.77734375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="10.109375" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="10.44140625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="10.109375" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="10.21875" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="10.44140625" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="10.109375" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="5" spans="2:10">
+      <c r="B5" s="4" t="s">
+        <v>36</v>
+      </c>
+      <c r="C5" s="4"/>
+      <c r="D5" s="5">
+        <f>C5/1.18</f>
+        <v>0</v>
+      </c>
+      <c r="E5" s="4">
+        <f>D5*0.18</f>
+        <v>0</v>
+      </c>
+      <c r="G5" t="s">
+        <v>4</v>
+      </c>
+      <c r="H5" s="4"/>
+    </row>
+    <row r="6" spans="2:10">
+      <c r="B6" s="4"/>
+      <c r="C6" s="4"/>
+      <c r="D6" s="5"/>
+      <c r="E6" s="4">
+        <f>E5-C9</f>
+        <v>-197.29</v>
+      </c>
+      <c r="G6" t="s">
+        <v>39</v>
+      </c>
+      <c r="H6" s="5"/>
+    </row>
+    <row r="7" spans="2:10">
+      <c r="B7" s="4" t="s">
+        <v>69</v>
+      </c>
+      <c r="C7" s="4"/>
+      <c r="D7" s="56"/>
+      <c r="E7" s="4"/>
+      <c r="G7" t="s">
+        <v>67</v>
+      </c>
+      <c r="H7" s="5"/>
+    </row>
+    <row r="8" spans="2:10">
+      <c r="B8" s="4" t="s">
+        <v>70</v>
+      </c>
+      <c r="C8" s="4">
+        <v>197.29</v>
+      </c>
+      <c r="D8" s="56"/>
+      <c r="E8" s="4"/>
+      <c r="H8" s="58">
+        <f>SUM(H5:H7)</f>
+        <v>0</v>
+      </c>
+      <c r="J8" s="9"/>
+    </row>
+    <row r="9" spans="2:10">
+      <c r="B9" s="4"/>
+      <c r="C9" s="5">
+        <f>SUM(C7:C8)</f>
+        <v>197.29</v>
+      </c>
+      <c r="D9" s="4"/>
+      <c r="E9" s="4"/>
+      <c r="H9" s="59"/>
+    </row>
+    <row r="10" spans="2:10">
+      <c r="G10" s="25" t="s">
+        <v>68</v>
+      </c>
+      <c r="H10" s="58"/>
+      <c r="I10" s="9"/>
+    </row>
+    <row r="11" spans="2:10">
+      <c r="C11" s="48"/>
+      <c r="H11" s="59"/>
+    </row>
+    <row r="12" spans="2:10">
+      <c r="H12" s="59"/>
+    </row>
+    <row r="13" spans="2:10">
+      <c r="H13" s="59"/>
+    </row>
+    <row r="14" spans="2:10">
+      <c r="H14" s="25"/>
+    </row>
+    <row r="15" spans="2:10">
+      <c r="H15" s="25"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1CC03B67-503D-428C-82C4-722BB660D290}">
   <dimension ref="C5:H19"/>
